--- a/Shablon/34461A.xlsx
+++ b/Shablon/34461A.xlsx
@@ -19,16 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="170">
-  <si>
-    <t>АО "Гос МКБ "Вымпел" им. И.И. Торопова"</t>
-  </si>
-  <si>
-    <t>125424, г.Москва, Волоколамское шоссе, дом 90, стр. 23</t>
-  </si>
-  <si>
-    <t>Тел.+7 (495) 491-05-31, 22-68, e-mail: ogmetr@vympelmkb.com</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="165">
   <si>
     <t>Условия проведения калибровки:</t>
   </si>
@@ -576,12 +567,6 @@
   </si>
   <si>
     <t>10 А</t>
-  </si>
-  <si>
-    <t>СГМетр, лаборатория средств электрических и радиотехнических измерений</t>
-  </si>
-  <si>
-    <t>Уникальный номер об аккредитации в реестре акредитованных лиц № РОСС СОБ 3.00231.2014</t>
   </si>
   <si>
     <t>Заключение:</t>
@@ -962,73 +947,60 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1038,43 +1010,56 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1389,72 +1374,62 @@
     <col min="2" max="3" width="11.7109375" style="3" customWidth="1"/>
     <col min="4" max="8" width="10.7109375" style="3" customWidth="1"/>
     <col min="9" max="9" width="9.42578125" style="3" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="83"/>
+    <col min="10" max="16384" width="9.140625" style="57"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="82" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
-      <c r="H1" s="82"/>
+      <c r="A1" s="69"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
       <c r="I1" s="7"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="82" t="s">
-        <v>165</v>
-      </c>
-      <c r="B2" s="82"/>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="82"/>
-      <c r="G2" s="82"/>
-      <c r="H2" s="82"/>
+      <c r="A2" s="69"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
       <c r="I2" s="7"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="82" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="82"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
+      <c r="A3" s="69"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="69"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="84" t="s">
-        <v>166</v>
-      </c>
-      <c r="B4" s="84"/>
-      <c r="C4" s="84"/>
-      <c r="D4" s="84"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="84"/>
-      <c r="G4" s="84"/>
-      <c r="H4" s="84"/>
+      <c r="A4" s="73"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
       <c r="I4" s="1"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="84" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
+      <c r="A5" s="73"/>
+      <c r="B5" s="73"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -1469,17 +1444,17 @@
       <c r="I6" s="1"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="81" t="str">
+      <c r="A7" s="78" t="str">
         <f>"Протокол поверки № 10/"&amp;C125&amp;"/"&amp;D10</f>
         <v>Протокол поверки № 10/_date/_numb</v>
       </c>
-      <c r="B7" s="81"/>
-      <c r="C7" s="81"/>
-      <c r="D7" s="81"/>
-      <c r="E7" s="81"/>
-      <c r="F7" s="81"/>
-      <c r="G7" s="81"/>
-      <c r="H7" s="81"/>
+      <c r="B7" s="78"/>
+      <c r="C7" s="78"/>
+      <c r="D7" s="78"/>
+      <c r="E7" s="78"/>
+      <c r="F7" s="78"/>
+      <c r="G7" s="78"/>
+      <c r="H7" s="78"/>
       <c r="I7" s="1"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -1494,29 +1469,29 @@
       <c r="I8" s="1"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="80" t="s">
-        <v>110</v>
-      </c>
-      <c r="B9" s="80"/>
-      <c r="C9" s="80"/>
+      <c r="A9" s="77" t="s">
+        <v>107</v>
+      </c>
+      <c r="B9" s="77"/>
+      <c r="C9" s="77"/>
       <c r="D9" s="35" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E9" s="36"/>
-      <c r="F9" s="85" t="s">
-        <v>42</v>
-      </c>
-      <c r="G9" s="85"/>
+      <c r="F9" s="58" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="58"/>
       <c r="H9" s="37"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="80" t="s">
-        <v>112</v>
-      </c>
-      <c r="B10" s="80"/>
-      <c r="C10" s="80"/>
-      <c r="D10" s="86" t="s">
-        <v>43</v>
+      <c r="A10" s="77" t="s">
+        <v>109</v>
+      </c>
+      <c r="B10" s="77"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="59" t="s">
+        <v>40</v>
       </c>
       <c r="E10" s="36"/>
       <c r="F10" s="36"/>
@@ -1524,11 +1499,11 @@
       <c r="H10" s="37"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="80" t="s">
-        <v>113</v>
-      </c>
-      <c r="B11" s="80"/>
-      <c r="C11" s="80"/>
+      <c r="A11" s="77" t="s">
+        <v>110</v>
+      </c>
+      <c r="B11" s="77"/>
+      <c r="C11" s="77"/>
       <c r="D11" s="35"/>
       <c r="E11" s="36"/>
       <c r="F11" s="36"/>
@@ -1536,11 +1511,11 @@
       <c r="H11" s="37"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="80" t="s">
-        <v>114</v>
-      </c>
-      <c r="B12" s="80"/>
-      <c r="C12" s="80"/>
+      <c r="A12" s="77" t="s">
+        <v>111</v>
+      </c>
+      <c r="B12" s="77"/>
+      <c r="C12" s="77"/>
       <c r="D12" s="38"/>
       <c r="E12" s="36"/>
       <c r="F12" s="36"/>
@@ -1548,13 +1523,13 @@
       <c r="H12" s="37"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="80" t="s">
-        <v>115</v>
-      </c>
-      <c r="B13" s="80"/>
-      <c r="C13" s="80"/>
-      <c r="D13" s="86" t="s">
-        <v>126</v>
+      <c r="A13" s="77" t="s">
+        <v>112</v>
+      </c>
+      <c r="B13" s="77"/>
+      <c r="C13" s="77"/>
+      <c r="D13" s="59" t="s">
+        <v>123</v>
       </c>
       <c r="E13" s="36"/>
       <c r="F13" s="36"/>
@@ -1562,13 +1537,13 @@
       <c r="H13" s="37"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="80" t="s">
-        <v>116</v>
-      </c>
-      <c r="B14" s="80"/>
-      <c r="C14" s="80"/>
+      <c r="A14" s="77" t="s">
+        <v>113</v>
+      </c>
+      <c r="B14" s="77"/>
+      <c r="C14" s="77"/>
       <c r="D14" s="39" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E14" s="36"/>
       <c r="F14" s="36"/>
@@ -1576,13 +1551,13 @@
       <c r="H14" s="37"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="80" t="s">
-        <v>118</v>
-      </c>
-      <c r="B15" s="80"/>
-      <c r="C15" s="80"/>
+      <c r="A15" s="77" t="s">
+        <v>115</v>
+      </c>
+      <c r="B15" s="77"/>
+      <c r="C15" s="77"/>
       <c r="D15" s="35" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E15" s="36"/>
       <c r="F15" s="36"/>
@@ -1590,104 +1565,104 @@
       <c r="H15" s="37"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B16" s="87"/>
+      <c r="B16" s="60"/>
       <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="71" t="s">
+      <c r="A18" s="74" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="75"/>
+      <c r="C18" s="76"/>
+      <c r="D18" s="71" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" s="71"/>
+      <c r="F18" s="71" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="71"/>
+      <c r="H18" s="9"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="81" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="79"/>
-      <c r="C18" s="72"/>
-      <c r="D18" s="78" t="s">
+      <c r="B19" s="82"/>
+      <c r="C19" s="83"/>
+      <c r="D19" s="72" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19" s="72"/>
+      <c r="F19" s="74" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="78"/>
-      <c r="F18" s="78" t="s">
+      <c r="G19" s="76"/>
+      <c r="H19" s="6"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="84" t="s">
         <v>29</v>
       </c>
-      <c r="G18" s="78"/>
-      <c r="H18" s="9"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="68" t="s">
+      <c r="B20" s="84"/>
+      <c r="C20" s="84"/>
+      <c r="D20" s="72" t="s">
+        <v>42</v>
+      </c>
+      <c r="E20" s="72"/>
+      <c r="F20" s="74" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="69"/>
-      <c r="C19" s="70"/>
-      <c r="D19" s="88" t="s">
-        <v>44</v>
-      </c>
-      <c r="E19" s="88"/>
-      <c r="F19" s="71" t="s">
+      <c r="G20" s="76"/>
+      <c r="H20" s="6"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="81" t="s">
         <v>31</v>
       </c>
-      <c r="G19" s="72"/>
-      <c r="H19" s="6"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="73" t="s">
+      <c r="B21" s="82"/>
+      <c r="C21" s="83"/>
+      <c r="D21" s="85" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" s="86"/>
+      <c r="F21" s="74" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="73"/>
-      <c r="C20" s="73"/>
-      <c r="D20" s="88" t="s">
-        <v>45</v>
-      </c>
-      <c r="E20" s="88"/>
-      <c r="F20" s="71" t="s">
+      <c r="G21" s="76"/>
+      <c r="H21" s="6"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="81" t="s">
         <v>33</v>
       </c>
-      <c r="G20" s="72"/>
-      <c r="H20" s="6"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="68" t="s">
+      <c r="B22" s="82"/>
+      <c r="C22" s="83"/>
+      <c r="D22" s="85"/>
+      <c r="E22" s="86"/>
+      <c r="F22" s="74" t="s">
         <v>34</v>
       </c>
-      <c r="B21" s="69"/>
-      <c r="C21" s="70"/>
-      <c r="D21" s="74" t="s">
-        <v>46</v>
-      </c>
-      <c r="E21" s="75"/>
-      <c r="F21" s="71" t="s">
+      <c r="G22" s="76"/>
+      <c r="H22" s="6"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="81" t="s">
+        <v>2</v>
+      </c>
+      <c r="B23" s="82"/>
+      <c r="C23" s="83"/>
+      <c r="D23" s="85"/>
+      <c r="E23" s="86"/>
+      <c r="F23" s="74" t="s">
         <v>35</v>
       </c>
-      <c r="G21" s="72"/>
-      <c r="H21" s="6"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="68" t="s">
-        <v>36</v>
-      </c>
-      <c r="B22" s="69"/>
-      <c r="C22" s="70"/>
-      <c r="D22" s="74"/>
-      <c r="E22" s="75"/>
-      <c r="F22" s="71" t="s">
-        <v>37</v>
-      </c>
-      <c r="G22" s="72"/>
-      <c r="H22" s="6"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="68" t="s">
-        <v>5</v>
-      </c>
-      <c r="B23" s="69"/>
-      <c r="C23" s="70"/>
-      <c r="D23" s="74"/>
-      <c r="E23" s="75"/>
-      <c r="F23" s="71" t="s">
-        <v>38</v>
-      </c>
-      <c r="G23" s="72"/>
+      <c r="G23" s="76"/>
       <c r="H23" s="6"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -1702,7 +1677,7 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B25" s="33"/>
       <c r="C25" s="33"/>
@@ -1724,17 +1699,17 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -1747,7 +1722,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -1759,52 +1734,52 @@
       <c r="I30" s="8"/>
     </row>
     <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="58" t="s">
+      <c r="A31" s="70" t="s">
+        <v>124</v>
+      </c>
+      <c r="B31" s="70" t="s">
+        <v>125</v>
+      </c>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70" t="s">
+        <v>126</v>
+      </c>
+      <c r="G31" s="70"/>
+      <c r="I31" s="9"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="70"/>
+      <c r="B32" s="70"/>
+      <c r="C32" s="70"/>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="49" t="s">
         <v>127</v>
       </c>
-      <c r="B31" s="58" t="s">
+      <c r="G32" s="49" t="s">
         <v>128</v>
       </c>
-      <c r="C31" s="58"/>
-      <c r="D31" s="58" t="s">
-        <v>4</v>
-      </c>
-      <c r="E31" s="58"/>
-      <c r="F31" s="58" t="s">
+      <c r="I32" s="9"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="70" t="s">
         <v>129</v>
-      </c>
-      <c r="G31" s="58"/>
-      <c r="I31" s="9"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="58"/>
-      <c r="B32" s="58"/>
-      <c r="C32" s="58"/>
-      <c r="D32" s="58"/>
-      <c r="E32" s="58"/>
-      <c r="F32" s="49" t="s">
-        <v>130</v>
-      </c>
-      <c r="G32" s="49" t="s">
-        <v>131</v>
-      </c>
-      <c r="I32" s="9"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="58" t="s">
-        <v>132</v>
       </c>
       <c r="B33" s="52">
         <v>100</v>
       </c>
-      <c r="C33" s="63" t="s">
-        <v>133</v>
-      </c>
-      <c r="D33" s="89" t="s">
-        <v>49</v>
-      </c>
-      <c r="E33" s="63" t="s">
-        <v>133</v>
+      <c r="C33" s="79" t="s">
+        <v>130</v>
+      </c>
+      <c r="D33" s="61" t="s">
+        <v>46</v>
+      </c>
+      <c r="E33" s="79" t="s">
+        <v>130</v>
       </c>
       <c r="F33" s="54">
         <f>100-0.0085</f>
@@ -1817,15 +1792,15 @@
       <c r="I33" s="6"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="58"/>
+      <c r="A34" s="70"/>
       <c r="B34" s="52">
         <v>-100</v>
       </c>
-      <c r="C34" s="63"/>
-      <c r="D34" s="89" t="s">
-        <v>50</v>
-      </c>
-      <c r="E34" s="63"/>
+      <c r="C34" s="79"/>
+      <c r="D34" s="61" t="s">
+        <v>47</v>
+      </c>
+      <c r="E34" s="79"/>
       <c r="F34" s="54">
         <f>-100-0.0085</f>
         <v>-100.0085</v>
@@ -1837,20 +1812,20 @@
       <c r="I34" s="6"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="58" t="s">
-        <v>134</v>
+      <c r="A35" s="70" t="s">
+        <v>131</v>
       </c>
       <c r="B35" s="52">
         <v>1</v>
       </c>
-      <c r="C35" s="63" t="s">
-        <v>135</v>
-      </c>
-      <c r="D35" s="89" t="s">
-        <v>51</v>
-      </c>
-      <c r="E35" s="60" t="s">
-        <v>135</v>
+      <c r="C35" s="79" t="s">
+        <v>132</v>
+      </c>
+      <c r="D35" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="E35" s="92" t="s">
+        <v>132</v>
       </c>
       <c r="F35" s="45">
         <f>1-0.000047</f>
@@ -1863,15 +1838,15 @@
       <c r="I35" s="6"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="58"/>
+      <c r="A36" s="70"/>
       <c r="B36" s="52">
         <v>-1</v>
       </c>
-      <c r="C36" s="63"/>
-      <c r="D36" s="89" t="s">
-        <v>52</v>
-      </c>
-      <c r="E36" s="60"/>
+      <c r="C36" s="79"/>
+      <c r="D36" s="61" t="s">
+        <v>49</v>
+      </c>
+      <c r="E36" s="92"/>
       <c r="F36" s="45">
         <f>-1-0.000047</f>
         <v>-1.0000469999999999</v>
@@ -1883,17 +1858,17 @@
       <c r="I36" s="6"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="58" t="s">
-        <v>136</v>
+      <c r="A37" s="70" t="s">
+        <v>133</v>
       </c>
       <c r="B37" s="52">
         <v>4</v>
       </c>
-      <c r="C37" s="63"/>
-      <c r="D37" s="89" t="s">
-        <v>53</v>
-      </c>
-      <c r="E37" s="60"/>
+      <c r="C37" s="79"/>
+      <c r="D37" s="61" t="s">
+        <v>50</v>
+      </c>
+      <c r="E37" s="92"/>
       <c r="F37" s="40">
         <f>4-0.00019</f>
         <v>3.9998100000000001</v>
@@ -1905,15 +1880,15 @@
       <c r="I37" s="6"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="58"/>
+      <c r="A38" s="70"/>
       <c r="B38" s="52">
         <v>10</v>
       </c>
-      <c r="C38" s="63"/>
-      <c r="D38" s="89" t="s">
-        <v>54</v>
-      </c>
-      <c r="E38" s="60"/>
+      <c r="C38" s="79"/>
+      <c r="D38" s="61" t="s">
+        <v>51</v>
+      </c>
+      <c r="E38" s="92"/>
       <c r="F38" s="54">
         <f>10-0.0004</f>
         <v>9.9995999999999992</v>
@@ -1925,15 +1900,15 @@
       <c r="I38" s="6"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="58"/>
+      <c r="A39" s="70"/>
       <c r="B39" s="52">
         <v>-10</v>
       </c>
-      <c r="C39" s="63"/>
-      <c r="D39" s="89" t="s">
-        <v>55</v>
-      </c>
-      <c r="E39" s="60"/>
+      <c r="C39" s="79"/>
+      <c r="D39" s="61" t="s">
+        <v>52</v>
+      </c>
+      <c r="E39" s="92"/>
       <c r="F39" s="54">
         <f>-10-0.0004</f>
         <v>-10.000400000000001</v>
@@ -1945,17 +1920,17 @@
       <c r="I39" s="6"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="58" t="s">
-        <v>137</v>
+      <c r="A40" s="70" t="s">
+        <v>134</v>
       </c>
       <c r="B40" s="52">
         <v>100</v>
       </c>
-      <c r="C40" s="63"/>
-      <c r="D40" s="89" t="s">
-        <v>56</v>
-      </c>
-      <c r="E40" s="60"/>
+      <c r="C40" s="79"/>
+      <c r="D40" s="61" t="s">
+        <v>53</v>
+      </c>
+      <c r="E40" s="92"/>
       <c r="F40" s="54">
         <f>100-0.0051</f>
         <v>99.994900000000001</v>
@@ -1967,15 +1942,15 @@
       <c r="I40" s="6"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="58"/>
+      <c r="A41" s="70"/>
       <c r="B41" s="52">
         <v>-100</v>
       </c>
-      <c r="C41" s="63"/>
-      <c r="D41" s="89" t="s">
-        <v>57</v>
-      </c>
-      <c r="E41" s="60"/>
+      <c r="C41" s="79"/>
+      <c r="D41" s="61" t="s">
+        <v>54</v>
+      </c>
+      <c r="E41" s="92"/>
       <c r="F41" s="54">
         <f>-100-0.0051</f>
         <v>-100.0051</v>
@@ -1987,17 +1962,17 @@
       <c r="I41" s="6"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="76" t="s">
-        <v>138</v>
+      <c r="A42" s="87" t="s">
+        <v>135</v>
       </c>
       <c r="B42" s="52">
         <v>1000</v>
       </c>
-      <c r="C42" s="63"/>
-      <c r="D42" s="89" t="s">
-        <v>58</v>
-      </c>
-      <c r="E42" s="60"/>
+      <c r="C42" s="79"/>
+      <c r="D42" s="61" t="s">
+        <v>55</v>
+      </c>
+      <c r="E42" s="92"/>
       <c r="F42" s="56">
         <f>1000-0.055</f>
         <v>999.94500000000005</v>
@@ -2009,15 +1984,15 @@
       <c r="I42" s="6"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="76"/>
+      <c r="A43" s="87"/>
       <c r="B43" s="52">
         <v>-500</v>
       </c>
-      <c r="C43" s="63"/>
-      <c r="D43" s="89" t="s">
-        <v>59</v>
-      </c>
-      <c r="E43" s="60"/>
+      <c r="C43" s="79"/>
+      <c r="D43" s="61" t="s">
+        <v>56</v>
+      </c>
+      <c r="E43" s="92"/>
       <c r="F43" s="54">
         <f>-500-0.0325</f>
         <v>-500.03250000000003</v>
@@ -2030,7 +2005,7 @@
     </row>
     <row r="45" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
@@ -2041,57 +2016,57 @@
       <c r="H45" s="8"/>
     </row>
     <row r="46" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="58" t="s">
+      <c r="A46" s="70" t="s">
+        <v>124</v>
+      </c>
+      <c r="B46" s="70" t="s">
+        <v>136</v>
+      </c>
+      <c r="C46" s="70"/>
+      <c r="D46" s="70" t="s">
+        <v>2</v>
+      </c>
+      <c r="E46" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70" t="s">
+        <v>126</v>
+      </c>
+      <c r="H46" s="70"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="70"/>
+      <c r="B47" s="70"/>
+      <c r="C47" s="70"/>
+      <c r="D47" s="70"/>
+      <c r="E47" s="70"/>
+      <c r="F47" s="70"/>
+      <c r="G47" s="49" t="s">
         <v>127</v>
       </c>
-      <c r="B46" s="58" t="s">
-        <v>139</v>
-      </c>
-      <c r="C46" s="58"/>
-      <c r="D46" s="58" t="s">
-        <v>5</v>
-      </c>
-      <c r="E46" s="58" t="s">
-        <v>4</v>
-      </c>
-      <c r="F46" s="58"/>
-      <c r="G46" s="58" t="s">
+      <c r="H47" s="49" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="88" t="s">
         <v>129</v>
       </c>
-      <c r="H46" s="58"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="58"/>
-      <c r="B47" s="58"/>
-      <c r="C47" s="58"/>
-      <c r="D47" s="58"/>
-      <c r="E47" s="58"/>
-      <c r="F47" s="58"/>
-      <c r="G47" s="49" t="s">
+      <c r="B48" s="89">
+        <v>100</v>
+      </c>
+      <c r="C48" s="90" t="s">
         <v>130</v>
       </c>
-      <c r="H47" s="49" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="66" t="s">
-        <v>132</v>
-      </c>
-      <c r="B48" s="65">
-        <v>100</v>
-      </c>
-      <c r="C48" s="64" t="s">
-        <v>133</v>
-      </c>
       <c r="D48" s="53" t="s">
-        <v>18</v>
-      </c>
-      <c r="E48" s="90" t="s">
-        <v>60</v>
-      </c>
-      <c r="F48" s="64" t="s">
-        <v>133</v>
+        <v>15</v>
+      </c>
+      <c r="E48" s="62" t="s">
+        <v>57</v>
+      </c>
+      <c r="F48" s="90" t="s">
+        <v>130</v>
       </c>
       <c r="G48" s="55">
         <f>100-0.09</f>
@@ -2103,16 +2078,16 @@
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="66"/>
-      <c r="B49" s="65"/>
-      <c r="C49" s="64"/>
+      <c r="A49" s="88"/>
+      <c r="B49" s="89"/>
+      <c r="C49" s="90"/>
       <c r="D49" s="53" t="s">
-        <v>20</v>
-      </c>
-      <c r="E49" s="90" t="s">
-        <v>61</v>
-      </c>
-      <c r="F49" s="64"/>
+        <v>17</v>
+      </c>
+      <c r="E49" s="62" t="s">
+        <v>58</v>
+      </c>
+      <c r="F49" s="90"/>
       <c r="G49" s="55">
         <f>100-0.17</f>
         <v>99.83</v>
@@ -2123,16 +2098,16 @@
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="66"/>
-      <c r="B50" s="65"/>
-      <c r="C50" s="64"/>
+      <c r="A50" s="88"/>
+      <c r="B50" s="89"/>
+      <c r="C50" s="90"/>
       <c r="D50" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="E50" s="90" t="s">
-        <v>62</v>
-      </c>
-      <c r="F50" s="64"/>
+        <v>22</v>
+      </c>
+      <c r="E50" s="62" t="s">
+        <v>59</v>
+      </c>
+      <c r="F50" s="90"/>
       <c r="G50" s="55">
         <f>100-4.5</f>
         <v>95.5</v>
@@ -2143,23 +2118,23 @@
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="57" t="s">
-        <v>134</v>
-      </c>
-      <c r="B51" s="65">
+      <c r="A51" s="91" t="s">
+        <v>131</v>
+      </c>
+      <c r="B51" s="89">
         <v>1</v>
       </c>
-      <c r="C51" s="64" t="s">
-        <v>135</v>
+      <c r="C51" s="90" t="s">
+        <v>132</v>
       </c>
       <c r="D51" s="53" t="s">
-        <v>18</v>
-      </c>
-      <c r="E51" s="90" t="s">
-        <v>63</v>
-      </c>
-      <c r="F51" s="64" t="s">
-        <v>135</v>
+        <v>15</v>
+      </c>
+      <c r="E51" s="62" t="s">
+        <v>60</v>
+      </c>
+      <c r="F51" s="90" t="s">
+        <v>132</v>
       </c>
       <c r="G51" s="54">
         <f>1-0.0009</f>
@@ -2171,16 +2146,16 @@
       </c>
     </row>
     <row r="52" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="57"/>
-      <c r="B52" s="65"/>
-      <c r="C52" s="64"/>
+      <c r="A52" s="91"/>
+      <c r="B52" s="89"/>
+      <c r="C52" s="90"/>
       <c r="D52" s="53" t="s">
-        <v>20</v>
-      </c>
-      <c r="E52" s="90" t="s">
-        <v>64</v>
-      </c>
-      <c r="F52" s="64"/>
+        <v>17</v>
+      </c>
+      <c r="E52" s="62" t="s">
+        <v>61</v>
+      </c>
+      <c r="F52" s="90"/>
       <c r="G52" s="56">
         <f>1-0.0017</f>
         <v>0.99829999999999997</v>
@@ -2191,16 +2166,16 @@
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="57"/>
-      <c r="B53" s="65"/>
-      <c r="C53" s="64"/>
+      <c r="A53" s="91"/>
+      <c r="B53" s="89"/>
+      <c r="C53" s="90"/>
       <c r="D53" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="E53" s="90" t="s">
-        <v>65</v>
-      </c>
-      <c r="F53" s="64"/>
+        <v>22</v>
+      </c>
+      <c r="E53" s="62" t="s">
+        <v>62</v>
+      </c>
+      <c r="F53" s="90"/>
       <c r="G53" s="56">
         <f>1-0.045</f>
         <v>0.95499999999999996</v>
@@ -2211,23 +2186,23 @@
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="57" t="s">
-        <v>136</v>
+      <c r="A54" s="91" t="s">
+        <v>133</v>
       </c>
       <c r="B54" s="53">
         <v>30</v>
       </c>
       <c r="C54" s="53" t="s">
-        <v>133</v>
-      </c>
-      <c r="D54" s="57" t="s">
-        <v>18</v>
-      </c>
-      <c r="E54" s="90" t="s">
-        <v>66</v>
+        <v>130</v>
+      </c>
+      <c r="D54" s="91" t="s">
+        <v>15</v>
+      </c>
+      <c r="E54" s="62" t="s">
+        <v>63</v>
       </c>
       <c r="F54" s="53" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="G54" s="56">
         <f>30-0.003</f>
@@ -2239,19 +2214,19 @@
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="57"/>
+      <c r="A55" s="91"/>
       <c r="B55" s="53">
         <v>1</v>
       </c>
-      <c r="C55" s="57" t="s">
-        <v>135</v>
-      </c>
-      <c r="D55" s="57"/>
-      <c r="E55" s="90" t="s">
-        <v>67</v>
-      </c>
-      <c r="F55" s="57" t="s">
-        <v>135</v>
+      <c r="C55" s="91" t="s">
+        <v>132</v>
+      </c>
+      <c r="D55" s="91"/>
+      <c r="E55" s="62" t="s">
+        <v>64</v>
+      </c>
+      <c r="F55" s="91" t="s">
+        <v>132</v>
       </c>
       <c r="G55" s="54">
         <f>1-0.0036</f>
@@ -2263,18 +2238,18 @@
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="57"/>
-      <c r="B56" s="57">
+      <c r="A56" s="91"/>
+      <c r="B56" s="91">
         <v>10</v>
       </c>
-      <c r="C56" s="57"/>
+      <c r="C56" s="91"/>
       <c r="D56" s="53" t="s">
-        <v>19</v>
-      </c>
-      <c r="E56" s="90" t="s">
-        <v>68</v>
-      </c>
-      <c r="F56" s="57"/>
+        <v>16</v>
+      </c>
+      <c r="E56" s="62" t="s">
+        <v>65</v>
+      </c>
+      <c r="F56" s="91"/>
       <c r="G56" s="56">
         <f>10-0.009</f>
         <v>9.9909999999999997</v>
@@ -2285,16 +2260,16 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="57"/>
-      <c r="B57" s="57"/>
-      <c r="C57" s="57"/>
+      <c r="A57" s="91"/>
+      <c r="B57" s="91"/>
+      <c r="C57" s="91"/>
       <c r="D57" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="E57" s="90" t="s">
-        <v>69</v>
-      </c>
-      <c r="F57" s="57"/>
+        <v>19</v>
+      </c>
+      <c r="E57" s="62" t="s">
+        <v>66</v>
+      </c>
+      <c r="F57" s="91"/>
       <c r="G57" s="56">
         <f>10-0.009</f>
         <v>9.9909999999999997</v>
@@ -2305,16 +2280,16 @@
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="57"/>
-      <c r="B58" s="57"/>
-      <c r="C58" s="57"/>
+      <c r="A58" s="91"/>
+      <c r="B58" s="91"/>
+      <c r="C58" s="91"/>
       <c r="D58" s="53" t="s">
-        <v>23</v>
-      </c>
-      <c r="E58" s="90" t="s">
-        <v>70</v>
-      </c>
-      <c r="F58" s="57"/>
+        <v>20</v>
+      </c>
+      <c r="E58" s="62" t="s">
+        <v>67</v>
+      </c>
+      <c r="F58" s="91"/>
       <c r="G58" s="56">
         <f>10-0.009</f>
         <v>9.9909999999999997</v>
@@ -2325,16 +2300,16 @@
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="57"/>
-      <c r="B59" s="57"/>
-      <c r="C59" s="57"/>
+      <c r="A59" s="91"/>
+      <c r="B59" s="91"/>
+      <c r="C59" s="91"/>
       <c r="D59" s="53" t="s">
-        <v>20</v>
-      </c>
-      <c r="E59" s="90" t="s">
-        <v>71</v>
-      </c>
-      <c r="F59" s="57"/>
+        <v>17</v>
+      </c>
+      <c r="E59" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F59" s="91"/>
       <c r="G59" s="55">
         <f>10-0.017</f>
         <v>9.9830000000000005</v>
@@ -2345,16 +2320,16 @@
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="57"/>
-      <c r="B60" s="57"/>
-      <c r="C60" s="57"/>
+      <c r="A60" s="91"/>
+      <c r="B60" s="91"/>
+      <c r="C60" s="91"/>
       <c r="D60" s="53" t="s">
-        <v>24</v>
-      </c>
-      <c r="E60" s="90" t="s">
-        <v>72</v>
-      </c>
-      <c r="F60" s="57"/>
+        <v>21</v>
+      </c>
+      <c r="E60" s="62" t="s">
+        <v>69</v>
+      </c>
+      <c r="F60" s="91"/>
       <c r="G60" s="56">
         <f>10-0.068</f>
         <v>9.9320000000000004</v>
@@ -2365,16 +2340,16 @@
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="57"/>
-      <c r="B61" s="57"/>
-      <c r="C61" s="57"/>
+      <c r="A61" s="91"/>
+      <c r="B61" s="91"/>
+      <c r="C61" s="91"/>
       <c r="D61" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="E61" s="90" t="s">
-        <v>73</v>
-      </c>
-      <c r="F61" s="57"/>
+        <v>22</v>
+      </c>
+      <c r="E61" s="62" t="s">
+        <v>70</v>
+      </c>
+      <c r="F61" s="91"/>
       <c r="G61" s="55">
         <f>10-0.45</f>
         <v>9.5500000000000007</v>
@@ -2385,23 +2360,23 @@
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="57" t="s">
-        <v>137</v>
-      </c>
-      <c r="B62" s="57">
+      <c r="A62" s="91" t="s">
+        <v>134</v>
+      </c>
+      <c r="B62" s="91">
         <v>100</v>
       </c>
-      <c r="C62" s="57" t="s">
-        <v>135</v>
+      <c r="C62" s="91" t="s">
+        <v>132</v>
       </c>
       <c r="D62" s="53" t="s">
-        <v>18</v>
-      </c>
-      <c r="E62" s="90" t="s">
-        <v>74</v>
-      </c>
-      <c r="F62" s="57" t="s">
-        <v>135</v>
+        <v>15</v>
+      </c>
+      <c r="E62" s="62" t="s">
+        <v>71</v>
+      </c>
+      <c r="F62" s="91" t="s">
+        <v>132</v>
       </c>
       <c r="G62" s="55">
         <f>100-0.09</f>
@@ -2413,16 +2388,16 @@
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="57"/>
-      <c r="B63" s="57"/>
-      <c r="C63" s="57"/>
+      <c r="A63" s="91"/>
+      <c r="B63" s="91"/>
+      <c r="C63" s="91"/>
       <c r="D63" s="53" t="s">
-        <v>20</v>
-      </c>
-      <c r="E63" s="90" t="s">
-        <v>75</v>
-      </c>
-      <c r="F63" s="57"/>
+        <v>17</v>
+      </c>
+      <c r="E63" s="62" t="s">
+        <v>72</v>
+      </c>
+      <c r="F63" s="91"/>
       <c r="G63" s="52">
         <f>100-0.17</f>
         <v>99.83</v>
@@ -2433,18 +2408,18 @@
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="57"/>
+      <c r="A64" s="91"/>
       <c r="B64" s="53">
         <v>70</v>
       </c>
-      <c r="C64" s="57"/>
+      <c r="C64" s="91"/>
       <c r="D64" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="E64" s="90" t="s">
-        <v>76</v>
-      </c>
-      <c r="F64" s="57"/>
+        <v>22</v>
+      </c>
+      <c r="E64" s="62" t="s">
+        <v>73</v>
+      </c>
+      <c r="F64" s="91"/>
       <c r="G64" s="52">
         <f>70-3.3</f>
         <v>66.7</v>
@@ -2455,23 +2430,23 @@
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="57" t="s">
-        <v>140</v>
+      <c r="A65" s="91" t="s">
+        <v>137</v>
       </c>
       <c r="B65" s="53">
         <v>750</v>
       </c>
-      <c r="C65" s="57" t="s">
-        <v>135</v>
+      <c r="C65" s="91" t="s">
+        <v>132</v>
       </c>
       <c r="D65" s="53" t="s">
-        <v>18</v>
-      </c>
-      <c r="E65" s="90" t="s">
-        <v>77</v>
-      </c>
-      <c r="F65" s="57" t="s">
-        <v>135</v>
+        <v>15</v>
+      </c>
+      <c r="E65" s="62" t="s">
+        <v>74</v>
+      </c>
+      <c r="F65" s="91" t="s">
+        <v>132</v>
       </c>
       <c r="G65" s="52">
         <f>750-0.675</f>
@@ -2483,18 +2458,18 @@
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="57"/>
+      <c r="A66" s="91"/>
       <c r="B66" s="53">
         <v>210</v>
       </c>
-      <c r="C66" s="57"/>
+      <c r="C66" s="91"/>
       <c r="D66" s="53" t="s">
-        <v>20</v>
-      </c>
-      <c r="E66" s="90" t="s">
-        <v>78</v>
-      </c>
-      <c r="F66" s="57"/>
+        <v>17</v>
+      </c>
+      <c r="E66" s="62" t="s">
+        <v>75</v>
+      </c>
+      <c r="F66" s="91"/>
       <c r="G66" s="55">
         <f>210-0.627</f>
         <v>209.37299999999999</v>
@@ -2505,18 +2480,18 @@
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="57"/>
+      <c r="A67" s="91"/>
       <c r="B67" s="53">
         <v>70</v>
       </c>
-      <c r="C67" s="57"/>
+      <c r="C67" s="91"/>
       <c r="D67" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="E67" s="90" t="s">
-        <v>79</v>
-      </c>
-      <c r="F67" s="57"/>
+        <v>22</v>
+      </c>
+      <c r="E67" s="62" t="s">
+        <v>76</v>
+      </c>
+      <c r="F67" s="91"/>
       <c r="G67" s="52">
         <f>70-6.6</f>
         <v>63.4</v>
@@ -2531,14 +2506,14 @@
       <c r="B68" s="11"/>
       <c r="C68" s="11"/>
       <c r="D68" s="11"/>
-      <c r="E68" s="91"/>
+      <c r="E68" s="63"/>
       <c r="F68" s="11"/>
       <c r="G68" s="47"/>
       <c r="H68" s="47"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="17" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B69" s="12"/>
       <c r="C69" s="13"/>
@@ -2547,50 +2522,50 @@
       <c r="F69" s="16"/>
     </row>
     <row r="70" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="58" t="s">
+      <c r="A70" s="70" t="s">
+        <v>124</v>
+      </c>
+      <c r="B70" s="70" t="s">
+        <v>136</v>
+      </c>
+      <c r="C70" s="70"/>
+      <c r="D70" s="70" t="s">
+        <v>138</v>
+      </c>
+      <c r="E70" s="70"/>
+      <c r="F70" s="70" t="s">
+        <v>126</v>
+      </c>
+      <c r="G70" s="70"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="70"/>
+      <c r="B71" s="70"/>
+      <c r="C71" s="70"/>
+      <c r="D71" s="70"/>
+      <c r="E71" s="70"/>
+      <c r="F71" s="49" t="s">
         <v>127</v>
       </c>
-      <c r="B70" s="58" t="s">
-        <v>139</v>
-      </c>
-      <c r="C70" s="58"/>
-      <c r="D70" s="58" t="s">
-        <v>141</v>
-      </c>
-      <c r="E70" s="58"/>
-      <c r="F70" s="58" t="s">
-        <v>129</v>
-      </c>
-      <c r="G70" s="58"/>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="58"/>
-      <c r="B71" s="58"/>
-      <c r="C71" s="58"/>
-      <c r="D71" s="58"/>
-      <c r="E71" s="58"/>
-      <c r="F71" s="49" t="s">
-        <v>130</v>
-      </c>
       <c r="G71" s="49" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="53" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B72" s="53">
         <v>100</v>
       </c>
       <c r="C72" s="51" t="s">
-        <v>143</v>
-      </c>
-      <c r="D72" s="90" t="s">
-        <v>80</v>
+        <v>140</v>
+      </c>
+      <c r="D72" s="62" t="s">
+        <v>77</v>
       </c>
       <c r="E72" s="51" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F72" s="56">
         <f>100-0.075</f>
@@ -2603,19 +2578,19 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="53" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B73" s="53">
         <v>1</v>
       </c>
-      <c r="C73" s="63" t="s">
-        <v>145</v>
-      </c>
-      <c r="D73" s="90" t="s">
-        <v>81</v>
-      </c>
-      <c r="E73" s="63" t="s">
-        <v>145</v>
+      <c r="C73" s="79" t="s">
+        <v>142</v>
+      </c>
+      <c r="D73" s="62" t="s">
+        <v>78</v>
+      </c>
+      <c r="E73" s="79" t="s">
+        <v>142</v>
       </c>
       <c r="F73" s="40">
         <f>1-0.00056</f>
@@ -2628,16 +2603,16 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="53" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B74" s="53">
         <v>10</v>
       </c>
-      <c r="C74" s="63"/>
-      <c r="D74" s="90" t="s">
-        <v>82</v>
-      </c>
-      <c r="E74" s="63"/>
+      <c r="C74" s="79"/>
+      <c r="D74" s="62" t="s">
+        <v>79</v>
+      </c>
+      <c r="E74" s="79"/>
       <c r="F74" s="56">
         <f>10-0.007</f>
         <v>9.9930000000000003</v>
@@ -2649,16 +2624,16 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="53" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B75" s="53">
         <v>100</v>
       </c>
-      <c r="C75" s="63"/>
-      <c r="D75" s="90" t="s">
-        <v>83</v>
-      </c>
-      <c r="E75" s="63"/>
+      <c r="C75" s="79"/>
+      <c r="D75" s="62" t="s">
+        <v>80</v>
+      </c>
+      <c r="E75" s="79"/>
       <c r="F75" s="56">
         <f>100-0.055</f>
         <v>99.944999999999993</v>
@@ -2670,19 +2645,19 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="53" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B76" s="53">
         <v>1</v>
       </c>
-      <c r="C76" s="63" t="s">
-        <v>149</v>
-      </c>
-      <c r="D76" s="90" t="s">
-        <v>84</v>
-      </c>
-      <c r="E76" s="63" t="s">
-        <v>149</v>
+      <c r="C76" s="79" t="s">
+        <v>146</v>
+      </c>
+      <c r="D76" s="62" t="s">
+        <v>81</v>
+      </c>
+      <c r="E76" s="79" t="s">
+        <v>146</v>
       </c>
       <c r="F76" s="54">
         <f>1-0.0011</f>
@@ -2695,16 +2670,16 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="53" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B77" s="53">
         <v>2</v>
       </c>
-      <c r="C77" s="63"/>
-      <c r="D77" s="90" t="s">
-        <v>85</v>
-      </c>
-      <c r="E77" s="63"/>
+      <c r="C77" s="79"/>
+      <c r="D77" s="62" t="s">
+        <v>82</v>
+      </c>
+      <c r="E77" s="79"/>
       <c r="F77" s="54">
         <f>2-0.0046</f>
         <v>1.9954000000000001</v>
@@ -2715,17 +2690,17 @@
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="57">
+      <c r="A78" s="91">
         <v>10</v>
       </c>
       <c r="B78" s="53">
         <v>5</v>
       </c>
-      <c r="C78" s="63"/>
-      <c r="D78" s="90" t="s">
-        <v>123</v>
-      </c>
-      <c r="E78" s="63"/>
+      <c r="C78" s="79"/>
+      <c r="D78" s="62" t="s">
+        <v>120</v>
+      </c>
+      <c r="E78" s="79"/>
       <c r="F78" s="56">
         <f>5-0.012</f>
         <v>4.9880000000000004</v>
@@ -2736,15 +2711,15 @@
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="57"/>
+      <c r="A79" s="91"/>
       <c r="B79" s="53">
         <v>10</v>
       </c>
-      <c r="C79" s="63"/>
-      <c r="D79" s="90" t="s">
-        <v>124</v>
-      </c>
-      <c r="E79" s="63"/>
+      <c r="C79" s="79"/>
+      <c r="D79" s="62" t="s">
+        <v>121</v>
+      </c>
+      <c r="E79" s="79"/>
       <c r="F79" s="56">
         <f>10-0.022</f>
         <v>9.9779999999999998</v>
@@ -2758,14 +2733,14 @@
       <c r="A80" s="11"/>
       <c r="B80" s="11"/>
       <c r="C80" s="48"/>
-      <c r="D80" s="91"/>
+      <c r="D80" s="63"/>
       <c r="E80" s="48"/>
       <c r="F80" s="16"/>
       <c r="G80" s="11"/>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="17" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B81" s="11"/>
       <c r="C81" s="13"/>
@@ -2774,24 +2749,24 @@
       <c r="F81" s="16"/>
     </row>
     <row r="82" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="58" t="s">
-        <v>127</v>
-      </c>
-      <c r="B82" s="58" t="s">
-        <v>139</v>
-      </c>
-      <c r="C82" s="58"/>
-      <c r="D82" s="58" t="s">
-        <v>5</v>
-      </c>
-      <c r="E82" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="F82" s="58"/>
-      <c r="G82" s="58" t="s">
-        <v>129</v>
-      </c>
-      <c r="H82" s="58"/>
+      <c r="A82" s="70" t="s">
+        <v>124</v>
+      </c>
+      <c r="B82" s="70" t="s">
+        <v>136</v>
+      </c>
+      <c r="C82" s="70"/>
+      <c r="D82" s="70" t="s">
+        <v>2</v>
+      </c>
+      <c r="E82" s="70" t="s">
+        <v>6</v>
+      </c>
+      <c r="F82" s="70"/>
+      <c r="G82" s="70" t="s">
+        <v>126</v>
+      </c>
+      <c r="H82" s="70"/>
       <c r="J82" s="41"/>
       <c r="K82" s="41"/>
       <c r="L82" s="41"/>
@@ -2800,17 +2775,17 @@
       <c r="O82" s="41"/>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A83" s="58"/>
-      <c r="B83" s="58"/>
-      <c r="C83" s="58"/>
-      <c r="D83" s="58"/>
-      <c r="E83" s="58"/>
-      <c r="F83" s="58"/>
+      <c r="A83" s="70"/>
+      <c r="B83" s="70"/>
+      <c r="C83" s="70"/>
+      <c r="D83" s="70"/>
+      <c r="E83" s="70"/>
+      <c r="F83" s="70"/>
       <c r="G83" s="49" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H83" s="49" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="J83" s="41"/>
       <c r="K83" s="41"/>
@@ -2820,131 +2795,131 @@
       <c r="O83" s="41"/>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A84" s="57" t="s">
-        <v>142</v>
-      </c>
-      <c r="B84" s="57">
+      <c r="A84" s="91" t="s">
+        <v>139</v>
+      </c>
+      <c r="B84" s="91">
         <v>100</v>
       </c>
-      <c r="C84" s="63" t="s">
-        <v>143</v>
+      <c r="C84" s="79" t="s">
+        <v>140</v>
       </c>
       <c r="D84" s="53" t="s">
-        <v>18</v>
-      </c>
-      <c r="E84" s="90" t="s">
-        <v>86</v>
-      </c>
-      <c r="F84" s="63" t="s">
-        <v>143</v>
-      </c>
-      <c r="G84" s="61">
+        <v>15</v>
+      </c>
+      <c r="E84" s="62" t="s">
+        <v>83</v>
+      </c>
+      <c r="F84" s="79" t="s">
+        <v>140</v>
+      </c>
+      <c r="G84" s="93">
         <f>100-0.14</f>
         <v>99.86</v>
       </c>
-      <c r="H84" s="61">
+      <c r="H84" s="93">
         <f>100+0.14</f>
         <v>100.14</v>
       </c>
       <c r="J84" s="42"/>
       <c r="K84" s="42"/>
       <c r="L84" s="42"/>
-      <c r="M84" s="92"/>
-      <c r="N84" s="92"/>
+      <c r="M84" s="64"/>
+      <c r="N84" s="64"/>
       <c r="O84" s="16"/>
     </row>
     <row r="85" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="57"/>
-      <c r="B85" s="57"/>
-      <c r="C85" s="63"/>
+      <c r="A85" s="91"/>
+      <c r="B85" s="91"/>
+      <c r="C85" s="79"/>
       <c r="D85" s="53" t="s">
-        <v>26</v>
-      </c>
-      <c r="E85" s="90" t="s">
-        <v>87</v>
-      </c>
-      <c r="F85" s="63"/>
-      <c r="G85" s="61"/>
-      <c r="H85" s="61"/>
+        <v>23</v>
+      </c>
+      <c r="E85" s="62" t="s">
+        <v>84</v>
+      </c>
+      <c r="F85" s="79"/>
+      <c r="G85" s="93"/>
+      <c r="H85" s="93"/>
       <c r="J85" s="6"/>
       <c r="K85" s="11"/>
       <c r="L85" s="11"/>
-      <c r="M85" s="92"/>
-      <c r="N85" s="92"/>
+      <c r="M85" s="64"/>
+      <c r="N85" s="64"/>
       <c r="O85" s="16"/>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A86" s="57" t="s">
-        <v>144</v>
-      </c>
-      <c r="B86" s="57">
+      <c r="A86" s="91" t="s">
+        <v>141</v>
+      </c>
+      <c r="B86" s="91">
         <v>1</v>
       </c>
-      <c r="C86" s="57" t="s">
-        <v>145</v>
+      <c r="C86" s="91" t="s">
+        <v>142</v>
       </c>
       <c r="D86" s="53" t="s">
-        <v>18</v>
-      </c>
-      <c r="E86" s="90" t="s">
-        <v>88</v>
-      </c>
-      <c r="F86" s="57" t="s">
-        <v>145</v>
-      </c>
-      <c r="G86" s="60">
+        <v>15</v>
+      </c>
+      <c r="E86" s="62" t="s">
+        <v>85</v>
+      </c>
+      <c r="F86" s="91" t="s">
+        <v>142</v>
+      </c>
+      <c r="G86" s="92">
         <f>1-0.0014</f>
         <v>0.99860000000000004</v>
       </c>
-      <c r="H86" s="57">
+      <c r="H86" s="91">
         <f>1+0.0014</f>
         <v>1.0014000000000001</v>
       </c>
       <c r="J86" s="6"/>
       <c r="K86" s="11"/>
       <c r="L86" s="11"/>
-      <c r="M86" s="92"/>
-      <c r="N86" s="92"/>
+      <c r="M86" s="64"/>
+      <c r="N86" s="64"/>
       <c r="O86" s="16"/>
     </row>
     <row r="87" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="57"/>
-      <c r="B87" s="57"/>
-      <c r="C87" s="57"/>
+      <c r="A87" s="91"/>
+      <c r="B87" s="91"/>
+      <c r="C87" s="91"/>
       <c r="D87" s="53" t="s">
-        <v>26</v>
-      </c>
-      <c r="E87" s="90" t="s">
-        <v>89</v>
-      </c>
-      <c r="F87" s="57"/>
-      <c r="G87" s="60"/>
-      <c r="H87" s="57"/>
+        <v>23</v>
+      </c>
+      <c r="E87" s="62" t="s">
+        <v>86</v>
+      </c>
+      <c r="F87" s="91"/>
+      <c r="G87" s="92"/>
+      <c r="H87" s="91"/>
       <c r="J87" s="6"/>
       <c r="K87" s="6"/>
       <c r="L87" s="11"/>
-      <c r="M87" s="92"/>
-      <c r="N87" s="92"/>
+      <c r="M87" s="64"/>
+      <c r="N87" s="64"/>
       <c r="O87" s="16"/>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A88" s="57" t="s">
-        <v>146</v>
+      <c r="A88" s="91" t="s">
+        <v>143</v>
       </c>
       <c r="B88" s="53">
         <v>100</v>
       </c>
       <c r="C88" s="53" t="s">
-        <v>143</v>
-      </c>
-      <c r="D88" s="57" t="s">
-        <v>18</v>
-      </c>
-      <c r="E88" s="90" t="s">
-        <v>90</v>
+        <v>140</v>
+      </c>
+      <c r="D88" s="91" t="s">
+        <v>15</v>
+      </c>
+      <c r="E88" s="62" t="s">
+        <v>87</v>
       </c>
       <c r="F88" s="53" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G88" s="52">
         <f>100-4.1</f>
@@ -2957,24 +2932,24 @@
       <c r="J88" s="6"/>
       <c r="K88" s="6"/>
       <c r="L88" s="11"/>
-      <c r="M88" s="92"/>
-      <c r="N88" s="92"/>
+      <c r="M88" s="64"/>
+      <c r="N88" s="64"/>
       <c r="O88" s="16"/>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A89" s="57"/>
+      <c r="A89" s="91"/>
       <c r="B89" s="53">
         <v>1</v>
       </c>
-      <c r="C89" s="57" t="s">
-        <v>145</v>
-      </c>
-      <c r="D89" s="57"/>
-      <c r="E89" s="90" t="s">
-        <v>91</v>
-      </c>
-      <c r="F89" s="57" t="s">
-        <v>145</v>
+      <c r="C89" s="91" t="s">
+        <v>142</v>
+      </c>
+      <c r="D89" s="91"/>
+      <c r="E89" s="62" t="s">
+        <v>88</v>
+      </c>
+      <c r="F89" s="91" t="s">
+        <v>142</v>
       </c>
       <c r="G89" s="56">
         <f>1-0.005</f>
@@ -2987,256 +2962,256 @@
       <c r="J89" s="6"/>
       <c r="K89" s="6"/>
       <c r="L89" s="11"/>
-      <c r="M89" s="92"/>
-      <c r="N89" s="92"/>
+      <c r="M89" s="64"/>
+      <c r="N89" s="64"/>
       <c r="O89" s="16"/>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A90" s="57"/>
-      <c r="B90" s="57">
+      <c r="A90" s="91"/>
+      <c r="B90" s="91">
         <v>10</v>
       </c>
-      <c r="C90" s="57"/>
-      <c r="D90" s="57"/>
-      <c r="E90" s="90" t="s">
-        <v>92</v>
-      </c>
-      <c r="F90" s="57"/>
-      <c r="G90" s="62">
+      <c r="C90" s="91"/>
+      <c r="D90" s="91"/>
+      <c r="E90" s="62" t="s">
+        <v>89</v>
+      </c>
+      <c r="F90" s="91"/>
+      <c r="G90" s="94">
         <f>10-0.014</f>
         <v>9.9860000000000007</v>
       </c>
-      <c r="H90" s="57">
+      <c r="H90" s="91">
         <f>10+0.014</f>
         <v>10.013999999999999</v>
       </c>
       <c r="J90" s="6"/>
       <c r="K90" s="11"/>
       <c r="L90" s="11"/>
-      <c r="M90" s="92"/>
-      <c r="N90" s="92"/>
+      <c r="M90" s="64"/>
+      <c r="N90" s="64"/>
       <c r="O90" s="16"/>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A91" s="57"/>
-      <c r="B91" s="57"/>
-      <c r="C91" s="57"/>
+      <c r="A91" s="91"/>
+      <c r="B91" s="91"/>
+      <c r="C91" s="91"/>
       <c r="D91" s="53" t="s">
-        <v>26</v>
-      </c>
-      <c r="E91" s="90" t="s">
-        <v>93</v>
-      </c>
-      <c r="F91" s="57"/>
-      <c r="G91" s="62"/>
-      <c r="H91" s="57"/>
+        <v>23</v>
+      </c>
+      <c r="E91" s="62" t="s">
+        <v>90</v>
+      </c>
+      <c r="F91" s="91"/>
+      <c r="G91" s="94"/>
+      <c r="H91" s="91"/>
       <c r="J91" s="6"/>
       <c r="K91" s="11"/>
       <c r="L91" s="11"/>
-      <c r="M91" s="92"/>
-      <c r="N91" s="92"/>
+      <c r="M91" s="64"/>
+      <c r="N91" s="64"/>
       <c r="O91" s="16"/>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A92" s="57" t="s">
-        <v>147</v>
-      </c>
-      <c r="B92" s="57">
+      <c r="A92" s="91" t="s">
+        <v>144</v>
+      </c>
+      <c r="B92" s="91">
         <v>100</v>
       </c>
-      <c r="C92" s="57" t="s">
-        <v>145</v>
+      <c r="C92" s="91" t="s">
+        <v>142</v>
       </c>
       <c r="D92" s="53" t="s">
-        <v>19</v>
-      </c>
-      <c r="E92" s="90" t="s">
-        <v>94</v>
-      </c>
-      <c r="F92" s="57" t="s">
-        <v>145</v>
-      </c>
-      <c r="G92" s="61">
+        <v>16</v>
+      </c>
+      <c r="E92" s="62" t="s">
+        <v>91</v>
+      </c>
+      <c r="F92" s="91" t="s">
+        <v>142</v>
+      </c>
+      <c r="G92" s="93">
         <f>100-0.14</f>
         <v>99.86</v>
       </c>
-      <c r="H92" s="57">
+      <c r="H92" s="91">
         <f>100+0.14</f>
         <v>100.14</v>
       </c>
       <c r="J92" s="6"/>
       <c r="K92" s="11"/>
       <c r="L92" s="11"/>
-      <c r="M92" s="92"/>
-      <c r="N92" s="92"/>
+      <c r="M92" s="64"/>
+      <c r="N92" s="64"/>
       <c r="O92" s="16"/>
     </row>
     <row r="93" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="57"/>
-      <c r="B93" s="57"/>
-      <c r="C93" s="57"/>
+      <c r="A93" s="91"/>
+      <c r="B93" s="91"/>
+      <c r="C93" s="91"/>
       <c r="D93" s="53" t="s">
-        <v>18</v>
-      </c>
-      <c r="E93" s="90" t="s">
-        <v>95</v>
-      </c>
-      <c r="F93" s="57"/>
-      <c r="G93" s="61"/>
-      <c r="H93" s="57"/>
+        <v>15</v>
+      </c>
+      <c r="E93" s="62" t="s">
+        <v>92</v>
+      </c>
+      <c r="F93" s="91"/>
+      <c r="G93" s="93"/>
+      <c r="H93" s="91"/>
       <c r="J93" s="6"/>
       <c r="K93" s="11"/>
       <c r="L93" s="11"/>
-      <c r="M93" s="92"/>
-      <c r="N93" s="92"/>
+      <c r="M93" s="64"/>
+      <c r="N93" s="64"/>
       <c r="O93" s="16"/>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A94" s="57"/>
-      <c r="B94" s="57"/>
-      <c r="C94" s="57"/>
+      <c r="A94" s="91"/>
+      <c r="B94" s="91"/>
+      <c r="C94" s="91"/>
       <c r="D94" s="53" t="s">
-        <v>26</v>
-      </c>
-      <c r="E94" s="90" t="s">
-        <v>96</v>
-      </c>
-      <c r="F94" s="57"/>
-      <c r="G94" s="61"/>
-      <c r="H94" s="57"/>
+        <v>23</v>
+      </c>
+      <c r="E94" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="F94" s="91"/>
+      <c r="G94" s="93"/>
+      <c r="H94" s="91"/>
       <c r="J94" s="6"/>
       <c r="K94" s="11"/>
       <c r="L94" s="11"/>
-      <c r="M94" s="92"/>
-      <c r="N94" s="92"/>
+      <c r="M94" s="64"/>
+      <c r="N94" s="64"/>
       <c r="O94" s="16"/>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A95" s="57" t="s">
-        <v>148</v>
-      </c>
-      <c r="B95" s="57">
+      <c r="A95" s="91" t="s">
+        <v>145</v>
+      </c>
+      <c r="B95" s="91">
         <v>1</v>
       </c>
-      <c r="C95" s="57" t="s">
-        <v>149</v>
+      <c r="C95" s="91" t="s">
+        <v>146</v>
       </c>
       <c r="D95" s="53" t="s">
-        <v>18</v>
-      </c>
-      <c r="E95" s="90" t="s">
-        <v>97</v>
-      </c>
-      <c r="F95" s="57" t="s">
-        <v>149</v>
-      </c>
-      <c r="G95" s="60">
+        <v>15</v>
+      </c>
+      <c r="E95" s="62" t="s">
+        <v>94</v>
+      </c>
+      <c r="F95" s="91" t="s">
+        <v>146</v>
+      </c>
+      <c r="G95" s="92">
         <f>1-0.0014</f>
         <v>0.99860000000000004</v>
       </c>
-      <c r="H95" s="57">
+      <c r="H95" s="91">
         <f>1+0.0014</f>
         <v>1.0014000000000001</v>
       </c>
       <c r="J95" s="6"/>
       <c r="K95" s="11"/>
       <c r="L95" s="11"/>
-      <c r="M95" s="92"/>
-      <c r="N95" s="92"/>
+      <c r="M95" s="64"/>
+      <c r="N95" s="64"/>
       <c r="O95" s="16"/>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A96" s="57"/>
-      <c r="B96" s="57"/>
-      <c r="C96" s="57"/>
+      <c r="A96" s="91"/>
+      <c r="B96" s="91"/>
+      <c r="C96" s="91"/>
       <c r="D96" s="53" t="s">
-        <v>26</v>
-      </c>
-      <c r="E96" s="90" t="s">
-        <v>98</v>
-      </c>
-      <c r="F96" s="57"/>
-      <c r="G96" s="60"/>
-      <c r="H96" s="57"/>
+        <v>23</v>
+      </c>
+      <c r="E96" s="62" t="s">
+        <v>95</v>
+      </c>
+      <c r="F96" s="91"/>
+      <c r="G96" s="92"/>
+      <c r="H96" s="91"/>
       <c r="J96" s="6"/>
       <c r="K96" s="11"/>
       <c r="L96" s="11"/>
-      <c r="M96" s="92"/>
-      <c r="N96" s="92"/>
+      <c r="M96" s="64"/>
+      <c r="N96" s="64"/>
       <c r="O96" s="16"/>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A97" s="57" t="s">
-        <v>150</v>
-      </c>
-      <c r="B97" s="57">
+      <c r="A97" s="91" t="s">
+        <v>147</v>
+      </c>
+      <c r="B97" s="91">
         <v>2</v>
       </c>
-      <c r="C97" s="57" t="s">
-        <v>149</v>
+      <c r="C97" s="91" t="s">
+        <v>146</v>
       </c>
       <c r="D97" s="53" t="s">
-        <v>18</v>
-      </c>
-      <c r="E97" s="90" t="s">
-        <v>99</v>
-      </c>
-      <c r="F97" s="57" t="s">
-        <v>149</v>
-      </c>
-      <c r="G97" s="60">
+        <v>15</v>
+      </c>
+      <c r="E97" s="62" t="s">
+        <v>96</v>
+      </c>
+      <c r="F97" s="91" t="s">
+        <v>146</v>
+      </c>
+      <c r="G97" s="92">
         <f>2-0.0058</f>
         <v>1.9942</v>
       </c>
-      <c r="H97" s="57">
+      <c r="H97" s="91">
         <f>2+0.0058</f>
         <v>2.0057999999999998</v>
       </c>
       <c r="J97" s="6"/>
       <c r="K97" s="11"/>
       <c r="L97" s="11"/>
-      <c r="M97" s="92"/>
-      <c r="N97" s="92"/>
+      <c r="M97" s="64"/>
+      <c r="N97" s="64"/>
       <c r="O97" s="16"/>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A98" s="57"/>
-      <c r="B98" s="57"/>
-      <c r="C98" s="57"/>
+      <c r="A98" s="91"/>
+      <c r="B98" s="91"/>
+      <c r="C98" s="91"/>
       <c r="D98" s="53" t="s">
-        <v>26</v>
-      </c>
-      <c r="E98" s="90" t="s">
-        <v>100</v>
-      </c>
-      <c r="F98" s="57"/>
-      <c r="G98" s="60"/>
-      <c r="H98" s="57"/>
+        <v>23</v>
+      </c>
+      <c r="E98" s="62" t="s">
+        <v>97</v>
+      </c>
+      <c r="F98" s="91"/>
+      <c r="G98" s="92"/>
+      <c r="H98" s="91"/>
       <c r="J98" s="6"/>
       <c r="K98" s="11"/>
       <c r="L98" s="11"/>
-      <c r="M98" s="92"/>
-      <c r="N98" s="92"/>
+      <c r="M98" s="64"/>
+      <c r="N98" s="64"/>
       <c r="O98" s="16"/>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="53" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B99" s="53">
         <v>10</v>
       </c>
       <c r="C99" s="53" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D99" s="53" t="s">
-        <v>26</v>
-      </c>
-      <c r="E99" s="90" t="s">
-        <v>125</v>
+        <v>23</v>
+      </c>
+      <c r="E99" s="62" t="s">
+        <v>122</v>
       </c>
       <c r="F99" s="53" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="G99" s="50">
         <f>10-0.019</f>
@@ -3249,8 +3224,8 @@
       <c r="J99" s="6"/>
       <c r="K99" s="11"/>
       <c r="L99" s="11"/>
-      <c r="M99" s="92"/>
-      <c r="N99" s="92"/>
+      <c r="M99" s="64"/>
+      <c r="N99" s="64"/>
       <c r="O99" s="16"/>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
@@ -3258,20 +3233,20 @@
       <c r="B100" s="11"/>
       <c r="C100" s="11"/>
       <c r="D100" s="11"/>
-      <c r="E100" s="91"/>
+      <c r="E100" s="63"/>
       <c r="F100" s="11"/>
       <c r="G100" s="29"/>
       <c r="H100" s="29"/>
       <c r="J100" s="6"/>
       <c r="K100" s="11"/>
       <c r="L100" s="11"/>
-      <c r="M100" s="92"/>
-      <c r="N100" s="92"/>
+      <c r="M100" s="64"/>
+      <c r="N100" s="64"/>
       <c r="O100" s="16"/>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B101" s="11"/>
       <c r="C101" s="11"/>
@@ -3280,57 +3255,57 @@
       <c r="F101" s="16"/>
     </row>
     <row r="102" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="58" t="s">
+      <c r="A102" s="70" t="s">
+        <v>124</v>
+      </c>
+      <c r="B102" s="95" t="s">
+        <v>136</v>
+      </c>
+      <c r="C102" s="70" t="s">
+        <v>10</v>
+      </c>
+      <c r="D102" s="70"/>
+      <c r="E102" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="F102" s="70"/>
+      <c r="G102" s="70" t="s">
+        <v>126</v>
+      </c>
+      <c r="H102" s="70"/>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A103" s="70"/>
+      <c r="B103" s="95"/>
+      <c r="C103" s="70"/>
+      <c r="D103" s="70"/>
+      <c r="E103" s="70"/>
+      <c r="F103" s="70"/>
+      <c r="G103" s="49" t="s">
         <v>127</v>
       </c>
-      <c r="B102" s="59" t="s">
-        <v>139</v>
-      </c>
-      <c r="C102" s="58" t="s">
-        <v>13</v>
-      </c>
-      <c r="D102" s="58"/>
-      <c r="E102" s="58" t="s">
-        <v>12</v>
-      </c>
-      <c r="F102" s="58"/>
-      <c r="G102" s="58" t="s">
-        <v>129</v>
-      </c>
-      <c r="H102" s="58"/>
-    </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A103" s="58"/>
-      <c r="B103" s="59"/>
-      <c r="C103" s="58"/>
-      <c r="D103" s="58"/>
-      <c r="E103" s="58"/>
-      <c r="F103" s="58"/>
-      <c r="G103" s="49" t="s">
-        <v>130</v>
-      </c>
       <c r="H103" s="49" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" s="49" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B104" s="49" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C104" s="22">
         <v>10</v>
       </c>
       <c r="D104" s="51" t="s">
-        <v>151</v>
-      </c>
-      <c r="E104" s="90" t="s">
-        <v>101</v>
+        <v>148</v>
+      </c>
+      <c r="E104" s="62" t="s">
+        <v>98</v>
       </c>
       <c r="F104" s="51" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G104" s="56">
         <f>10-0.003</f>
@@ -3343,22 +3318,22 @@
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" s="49" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B105" s="49" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C105" s="22">
         <v>300</v>
       </c>
       <c r="D105" s="51" t="s">
-        <v>153</v>
-      </c>
-      <c r="E105" s="90" t="s">
-        <v>102</v>
+        <v>150</v>
+      </c>
+      <c r="E105" s="62" t="s">
+        <v>99</v>
       </c>
       <c r="F105" s="51" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G105" s="52">
         <f>300-0.3</f>
@@ -3369,12 +3344,12 @@
         <v>300.3</v>
       </c>
     </row>
-    <row r="106" spans="1:15" s="93" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="43"/>
       <c r="B106" s="42"/>
       <c r="C106" s="42"/>
-      <c r="D106" s="92"/>
-      <c r="E106" s="92"/>
+      <c r="D106" s="64"/>
+      <c r="E106" s="64"/>
       <c r="F106" s="42"/>
       <c r="G106" s="10"/>
       <c r="H106" s="10"/>
@@ -3382,7 +3357,7 @@
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B107" s="11"/>
       <c r="C107" s="11"/>
@@ -3392,7 +3367,7 @@
     </row>
     <row r="108" spans="1:15" s="5" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="5" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B108" s="18"/>
       <c r="C108" s="18"/>
@@ -3401,50 +3376,50 @@
       <c r="F108" s="21"/>
     </row>
     <row r="109" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="58" t="s">
+      <c r="A109" s="70" t="s">
+        <v>124</v>
+      </c>
+      <c r="B109" s="70" t="s">
+        <v>136</v>
+      </c>
+      <c r="C109" s="70"/>
+      <c r="D109" s="70" t="s">
+        <v>11</v>
+      </c>
+      <c r="E109" s="70"/>
+      <c r="F109" s="70" t="s">
+        <v>126</v>
+      </c>
+      <c r="G109" s="70"/>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A110" s="70"/>
+      <c r="B110" s="70"/>
+      <c r="C110" s="70"/>
+      <c r="D110" s="70"/>
+      <c r="E110" s="70"/>
+      <c r="F110" s="49" t="s">
         <v>127</v>
       </c>
-      <c r="B109" s="58" t="s">
-        <v>139</v>
-      </c>
-      <c r="C109" s="58"/>
-      <c r="D109" s="58" t="s">
-        <v>14</v>
-      </c>
-      <c r="E109" s="58"/>
-      <c r="F109" s="58" t="s">
-        <v>129</v>
-      </c>
-      <c r="G109" s="58"/>
-    </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A110" s="58"/>
-      <c r="B110" s="58"/>
-      <c r="C110" s="58"/>
-      <c r="D110" s="58"/>
-      <c r="E110" s="58"/>
-      <c r="F110" s="49" t="s">
-        <v>130</v>
-      </c>
       <c r="G110" s="49" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111" s="22" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B111" s="22">
         <v>100</v>
       </c>
       <c r="C111" s="51" t="s">
-        <v>155</v>
-      </c>
-      <c r="D111" s="90" t="s">
-        <v>103</v>
+        <v>152</v>
+      </c>
+      <c r="D111" s="62" t="s">
+        <v>100</v>
       </c>
       <c r="E111" s="51" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F111" s="56">
         <f>100-0.014</f>
@@ -3457,19 +3432,19 @@
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" s="22" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B112" s="22">
         <v>1</v>
       </c>
-      <c r="C112" s="63" t="s">
-        <v>157</v>
-      </c>
-      <c r="D112" s="90" t="s">
-        <v>104</v>
-      </c>
-      <c r="E112" s="63" t="s">
-        <v>157</v>
+      <c r="C112" s="79" t="s">
+        <v>154</v>
+      </c>
+      <c r="D112" s="62" t="s">
+        <v>101</v>
+      </c>
+      <c r="E112" s="79" t="s">
+        <v>154</v>
       </c>
       <c r="F112" s="40">
         <f>1-0.00011</f>
@@ -3482,16 +3457,16 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="22" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B113" s="22">
         <v>10</v>
       </c>
-      <c r="C113" s="63"/>
-      <c r="D113" s="90" t="s">
-        <v>105</v>
-      </c>
-      <c r="E113" s="63"/>
+      <c r="C113" s="79"/>
+      <c r="D113" s="62" t="s">
+        <v>102</v>
+      </c>
+      <c r="E113" s="79"/>
       <c r="F113" s="54">
         <f>10-0.0011</f>
         <v>9.9989000000000008</v>
@@ -3503,16 +3478,16 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="22" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B114" s="22">
         <v>100</v>
       </c>
-      <c r="C114" s="63"/>
-      <c r="D114" s="90" t="s">
-        <v>106</v>
-      </c>
-      <c r="E114" s="63"/>
+      <c r="C114" s="79"/>
+      <c r="D114" s="62" t="s">
+        <v>103</v>
+      </c>
+      <c r="E114" s="79"/>
       <c r="F114" s="56">
         <f>100-0.011</f>
         <v>99.989000000000004</v>
@@ -3532,7 +3507,7 @@
     </row>
     <row r="116" spans="1:9" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="28" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B116" s="18"/>
       <c r="C116" s="18"/>
@@ -3541,50 +3516,50 @@
       <c r="F116" s="21"/>
     </row>
     <row r="117" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="58" t="s">
+      <c r="A117" s="70" t="s">
+        <v>124</v>
+      </c>
+      <c r="B117" s="70" t="s">
+        <v>136</v>
+      </c>
+      <c r="C117" s="70"/>
+      <c r="D117" s="70" t="s">
+        <v>138</v>
+      </c>
+      <c r="E117" s="70"/>
+      <c r="F117" s="70" t="s">
+        <v>126</v>
+      </c>
+      <c r="G117" s="70"/>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A118" s="70"/>
+      <c r="B118" s="70"/>
+      <c r="C118" s="70"/>
+      <c r="D118" s="70"/>
+      <c r="E118" s="70"/>
+      <c r="F118" s="49" t="s">
         <v>127</v>
       </c>
-      <c r="B117" s="58" t="s">
-        <v>139</v>
-      </c>
-      <c r="C117" s="58"/>
-      <c r="D117" s="58" t="s">
-        <v>141</v>
-      </c>
-      <c r="E117" s="58"/>
-      <c r="F117" s="58" t="s">
-        <v>129</v>
-      </c>
-      <c r="G117" s="58"/>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A118" s="58"/>
-      <c r="B118" s="58"/>
-      <c r="C118" s="58"/>
-      <c r="D118" s="58"/>
-      <c r="E118" s="58"/>
-      <c r="F118" s="49" t="s">
-        <v>130</v>
-      </c>
       <c r="G118" s="49" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="22" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B119" s="22">
         <v>1</v>
       </c>
-      <c r="C119" s="63" t="s">
-        <v>161</v>
-      </c>
-      <c r="D119" s="90" t="s">
-        <v>107</v>
-      </c>
-      <c r="E119" s="63" t="s">
-        <v>161</v>
+      <c r="C119" s="79" t="s">
+        <v>158</v>
+      </c>
+      <c r="D119" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="E119" s="79" t="s">
+        <v>158</v>
       </c>
       <c r="F119" s="40">
         <f>1-0.00011</f>
@@ -3597,16 +3572,16 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="22" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B120" s="22">
         <v>10</v>
       </c>
-      <c r="C120" s="63"/>
-      <c r="D120" s="90" t="s">
-        <v>108</v>
-      </c>
-      <c r="E120" s="63"/>
+      <c r="C120" s="79"/>
+      <c r="D120" s="62" t="s">
+        <v>105</v>
+      </c>
+      <c r="E120" s="79"/>
       <c r="F120" s="54">
         <f>10-0.0041</f>
         <v>9.9959000000000007</v>
@@ -3618,16 +3593,16 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="22" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B121" s="22">
         <v>100</v>
       </c>
-      <c r="C121" s="63"/>
-      <c r="D121" s="90" t="s">
-        <v>109</v>
-      </c>
-      <c r="E121" s="63"/>
+      <c r="C121" s="79"/>
+      <c r="D121" s="62" t="s">
+        <v>106</v>
+      </c>
+      <c r="E121" s="79"/>
       <c r="F121" s="56">
         <f>100-0.081</f>
         <v>99.918999999999997</v>
@@ -3637,11 +3612,11 @@
         <v>100.081</v>
       </c>
     </row>
-    <row r="122" spans="1:9" s="93" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="27"/>
       <c r="B122" s="27"/>
-      <c r="C122" s="92"/>
-      <c r="D122" s="92"/>
+      <c r="C122" s="64"/>
+      <c r="D122" s="64"/>
       <c r="E122" s="16"/>
       <c r="F122" s="16"/>
       <c r="G122" s="10"/>
@@ -3649,50 +3624,168 @@
       <c r="I122" s="10"/>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A123" s="67" t="s">
-        <v>167</v>
-      </c>
-      <c r="B123" s="67"/>
+      <c r="A123" s="66" t="s">
+        <v>162</v>
+      </c>
+      <c r="B123" s="66"/>
       <c r="C123" s="46" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D123" s="10"/>
       <c r="E123" s="10"/>
       <c r="F123" s="16"/>
-      <c r="I123" s="83"/>
+      <c r="I123" s="57"/>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A124" s="67" t="s">
-        <v>169</v>
-      </c>
-      <c r="B124" s="67"/>
+      <c r="A124" s="66" t="s">
+        <v>164</v>
+      </c>
+      <c r="B124" s="66"/>
       <c r="C124" s="30"/>
       <c r="D124" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="E124" s="94" t="s">
-        <v>47</v>
-      </c>
-      <c r="F124" s="77"/>
+        <v>13</v>
+      </c>
+      <c r="E124" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="F124" s="68"/>
       <c r="G124" s="10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H124" s="32"/>
-      <c r="I124" s="83"/>
+      <c r="I124" s="57"/>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A125" s="67" t="s">
-        <v>15</v>
-      </c>
-      <c r="B125" s="67"/>
-      <c r="C125" s="95" t="s">
-        <v>48</v>
-      </c>
-      <c r="D125" s="95"/>
-      <c r="I125" s="83"/>
+      <c r="A125" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="B125" s="66"/>
+      <c r="C125" s="80" t="s">
+        <v>45</v>
+      </c>
+      <c r="D125" s="80"/>
+      <c r="I125" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="142">
+    <mergeCell ref="H97:H98"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="C102:D103"/>
+    <mergeCell ref="E102:F103"/>
+    <mergeCell ref="G102:H102"/>
+    <mergeCell ref="A97:A98"/>
+    <mergeCell ref="B97:B98"/>
+    <mergeCell ref="C97:C98"/>
+    <mergeCell ref="F97:F98"/>
+    <mergeCell ref="G97:G98"/>
+    <mergeCell ref="H92:H94"/>
+    <mergeCell ref="A95:A96"/>
+    <mergeCell ref="B95:B96"/>
+    <mergeCell ref="C95:C96"/>
+    <mergeCell ref="F95:F96"/>
+    <mergeCell ref="G95:G96"/>
+    <mergeCell ref="H95:H96"/>
+    <mergeCell ref="A92:A94"/>
+    <mergeCell ref="B92:B94"/>
+    <mergeCell ref="C92:C94"/>
+    <mergeCell ref="F92:F94"/>
+    <mergeCell ref="G92:G94"/>
+    <mergeCell ref="G86:G87"/>
+    <mergeCell ref="H86:H87"/>
+    <mergeCell ref="A88:A91"/>
+    <mergeCell ref="D88:D90"/>
+    <mergeCell ref="C89:C91"/>
+    <mergeCell ref="F89:F91"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="G90:G91"/>
+    <mergeCell ref="H90:H91"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="F84:F85"/>
+    <mergeCell ref="G84:G85"/>
+    <mergeCell ref="H84:H85"/>
+    <mergeCell ref="F70:G70"/>
+    <mergeCell ref="C73:C75"/>
+    <mergeCell ref="E73:E75"/>
+    <mergeCell ref="C76:C79"/>
+    <mergeCell ref="E76:E79"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="B70:C71"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="C35:C43"/>
+    <mergeCell ref="E35:E43"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="C62:C64"/>
+    <mergeCell ref="F62:F64"/>
+    <mergeCell ref="A65:A67"/>
+    <mergeCell ref="C65:C67"/>
+    <mergeCell ref="F65:F67"/>
+    <mergeCell ref="C51:C53"/>
+    <mergeCell ref="F51:F53"/>
+    <mergeCell ref="A54:A61"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="C55:C61"/>
+    <mergeCell ref="F55:F61"/>
+    <mergeCell ref="B56:B61"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="B46:C47"/>
+    <mergeCell ref="E46:F47"/>
+    <mergeCell ref="A51:A53"/>
+    <mergeCell ref="B51:B53"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="A48:A50"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="C48:C50"/>
+    <mergeCell ref="F48:F50"/>
+    <mergeCell ref="A123:B123"/>
+    <mergeCell ref="D70:E71"/>
+    <mergeCell ref="B82:C83"/>
+    <mergeCell ref="E82:F83"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="F86:F87"/>
+    <mergeCell ref="A117:A118"/>
+    <mergeCell ref="B117:C118"/>
+    <mergeCell ref="D117:E118"/>
+    <mergeCell ref="F117:G117"/>
+    <mergeCell ref="C119:C121"/>
+    <mergeCell ref="E119:E121"/>
+    <mergeCell ref="B109:C110"/>
+    <mergeCell ref="D109:E110"/>
+    <mergeCell ref="F109:G109"/>
+    <mergeCell ref="C112:C114"/>
+    <mergeCell ref="G82:H82"/>
+    <mergeCell ref="E112:E114"/>
+    <mergeCell ref="A125:B125"/>
+    <mergeCell ref="C125:D125"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A37:A39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="A109:A110"/>
+    <mergeCell ref="D82:D83"/>
+    <mergeCell ref="A70:A71"/>
     <mergeCell ref="A124:B124"/>
     <mergeCell ref="E124:F124"/>
     <mergeCell ref="A2:H2"/>
@@ -3717,124 +3810,6 @@
     <mergeCell ref="B31:C32"/>
     <mergeCell ref="D31:E32"/>
     <mergeCell ref="F31:G31"/>
-    <mergeCell ref="E112:E114"/>
-    <mergeCell ref="A125:B125"/>
-    <mergeCell ref="C125:D125"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="A37:A39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="E33:E34"/>
-    <mergeCell ref="A109:A110"/>
-    <mergeCell ref="D82:D83"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="G46:H46"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="C48:C50"/>
-    <mergeCell ref="F48:F50"/>
-    <mergeCell ref="A123:B123"/>
-    <mergeCell ref="D70:E71"/>
-    <mergeCell ref="B82:C83"/>
-    <mergeCell ref="E82:F83"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="C86:C87"/>
-    <mergeCell ref="F86:F87"/>
-    <mergeCell ref="A117:A118"/>
-    <mergeCell ref="B117:C118"/>
-    <mergeCell ref="D117:E118"/>
-    <mergeCell ref="F117:G117"/>
-    <mergeCell ref="C119:C121"/>
-    <mergeCell ref="E119:E121"/>
-    <mergeCell ref="B109:C110"/>
-    <mergeCell ref="D109:E110"/>
-    <mergeCell ref="F109:G109"/>
-    <mergeCell ref="C112:C114"/>
-    <mergeCell ref="G82:H82"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="C35:C43"/>
-    <mergeCell ref="E35:E43"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="C62:C64"/>
-    <mergeCell ref="F62:F64"/>
-    <mergeCell ref="A65:A67"/>
-    <mergeCell ref="C65:C67"/>
-    <mergeCell ref="F65:F67"/>
-    <mergeCell ref="C51:C53"/>
-    <mergeCell ref="F51:F53"/>
-    <mergeCell ref="A54:A61"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="C55:C61"/>
-    <mergeCell ref="F55:F61"/>
-    <mergeCell ref="B56:B61"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="B46:C47"/>
-    <mergeCell ref="E46:F47"/>
-    <mergeCell ref="A51:A53"/>
-    <mergeCell ref="B51:B53"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="F84:F85"/>
-    <mergeCell ref="G84:G85"/>
-    <mergeCell ref="H84:H85"/>
-    <mergeCell ref="F70:G70"/>
-    <mergeCell ref="C73:C75"/>
-    <mergeCell ref="E73:E75"/>
-    <mergeCell ref="C76:C79"/>
-    <mergeCell ref="E76:E79"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="B70:C71"/>
-    <mergeCell ref="G86:G87"/>
-    <mergeCell ref="H86:H87"/>
-    <mergeCell ref="A88:A91"/>
-    <mergeCell ref="D88:D90"/>
-    <mergeCell ref="C89:C91"/>
-    <mergeCell ref="F89:F91"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="G90:G91"/>
-    <mergeCell ref="H90:H91"/>
-    <mergeCell ref="H92:H94"/>
-    <mergeCell ref="A95:A96"/>
-    <mergeCell ref="B95:B96"/>
-    <mergeCell ref="C95:C96"/>
-    <mergeCell ref="F95:F96"/>
-    <mergeCell ref="G95:G96"/>
-    <mergeCell ref="H95:H96"/>
-    <mergeCell ref="A92:A94"/>
-    <mergeCell ref="B92:B94"/>
-    <mergeCell ref="C92:C94"/>
-    <mergeCell ref="F92:F94"/>
-    <mergeCell ref="G92:G94"/>
-    <mergeCell ref="H97:H98"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="C102:D103"/>
-    <mergeCell ref="E102:F103"/>
-    <mergeCell ref="G102:H102"/>
-    <mergeCell ref="A97:A98"/>
-    <mergeCell ref="B97:B98"/>
-    <mergeCell ref="C97:C98"/>
-    <mergeCell ref="F97:F98"/>
-    <mergeCell ref="G97:G98"/>
   </mergeCells>
   <pageMargins left="0.78740157480314965" right="0.39370078740157483" top="0.39370078740157483" bottom="0.61635416666666665" header="0.39370078740157483" footer="0.39370078740157483"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180" r:id="rId1"/>
